--- a/medford_osvetiteli_endoskopicheskie.xlsx
+++ b/medford_osvetiteli_endoskopicheskie.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Осветители эндоскопические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, GE, Olympus, MGB, Pentax — всего 12 позиций.</t>
+          <t>Осветители эндоскопические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, GE, Olympus, MGB, Pentax.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_osvetiteli_endoskopicheskie.xlsx
+++ b/medford_osvetiteli_endoskopicheskie.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать осветители эндоскопические для клиники?</t>
+          <t>Как подобрать осветитель под мой световод?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Производитель, Класс и тип безопасности, Время работы, часов, Источник света). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Совместимость определяется типом разъёма световодного кабеля — Karl Storz, Richard Wolf, Olympus и другие. Сначала уточняют, какой световод есть в отделении, и подбирают осветитель под его разъём либо планируют кабель под выбранный источник. Тип разъёма конкретной модели сверяют по документации до покупки, иначе потребуется переходник или замена кабеля.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Что лучше: LED или ксеноновый осветитель?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Светодиодные (LED) модели служат дольше и потребляют меньше энергии; у Mindray HB300L ресурс диода 60 000 часов. Ксеноновые и галогенные источники дают мощный поток, но лампа расходуется быстрее и требует замены. LED удобнее по стоимости владения, ламповые выбирают, когда нужен максимальный световой поток. Выбор зависит от задач и бюджета эксплуатации.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Сколько света нужно для эндоскопии?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Mindray, GE, Olympus, MGB, Pentax. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Требуемый световой поток зависит от задачи: для диагностических процедур обычно достаточно меньшей яркости, для хирургических вмешательств выбирают более мощные источники. Конкретное значение в люксах уточняют по спецификации модели и согласуют с типом эндоскопа. Профиль применения отделения определяет, какой запас по яркости целесообразен, поэтому характеристики сверяют заранее.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какой ресурс у эндоскопического осветителя?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>У светодиодных источников ресурс диода измеряется десятками тысяч часов: Mindray HB300L — 60 000, HB200L — 20 000 часов. У ксеноновых и галогенных ламп ресурс ниже и требует периодической замены лампы. Ресурс влияет на стоимость владения и частоту обслуживания, поэтому его сверяют по спецификации конкретной модели перед покупкой.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Что означает цветовая температура источника?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Цветовая температура задаёт оттенок света и влияет на восприятие тканей при осмотре. У светодиодных Mindray HB300L и HB200L она регулируется в диапазоне 3000–7000 К, что позволяет подстроить свет под задачу. Диапазон и возможность регулировки различаются у моделей, поэтому их уточняют по документации выбранного осветителя.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Что такое класс I, тип BF?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Это обозначения электробезопасности медицинского изделия: класс I описывает способ защиты от поражения током, тип BF — степень защиты рабочей части, контактирующей с пациентом. Модели MGB отнесены к классу I, тип BF. Класс и тип безопасности важны для допуска оборудования в эксплуатацию и указываются в характеристиках конкретной модели.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>osvetiteli_endoskopicheskie</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Да. Эндоскопический осветитель — медицинское изделие, вводимое в оборот при действующем регистрационном удостоверении Росздравнадзора на модель. Перед приобретением сверяют статус РУ, совместимость разъёма со световодом, класс электробезопасности и условия сервиса, а для ламповых источников — доступность сменных ксеноновых или галогенных ламп у поставщика.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>osvetiteli_endoskopicheskie</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Осветители эндоскопические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, GE, Olympus, MGB, Pentax.</t>
+          <t>Осветители эндоскопические — источники света, которые по световодному кабелю подают световой поток в полость для визуализации при эндоскопии. В каталоге собраны светодиодные и ксеноновые модели Mindray, Olympus, Pentax, HUGER, MGB и НПФ Крыло. Светодиодные источники Mindray HB300L и HB200L имеют цветовую температуру 3000–7000 К и ресурс диода 60 000 и 20 000 часов соответственно. Ксеноновые и галогенные модели MGB представлены мощностью 180 и 300 Вт с классом безопасности I, тип BF. Ключевой практический параметр — совместимость разъёма с имеющимся световодом.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы эндоскопических осветителей</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое осветители эндоскопические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3746,247 +3822,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы эндоскопических осветителей</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Признак</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Светодиодные (LED)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Класс и тип безопасности</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Время работы, часов</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Источник света</t>
+          <t>Ксеноновые / галогенные</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопический источник света Mindray HB300L</t>
+          <t>Ресурс</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
+          <t>десятки тысяч часов (HB300L — 60 000 ч)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Светодиодный (LED)</t>
+          <t>ниже, лампа требует замены</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Осветитель эндоскопический HUGER LLS-2100P (LED)</t>
+          <t>Энергопотребление</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>ниже</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>58589</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>выше</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Осветитель эндоскопический Olympus CLV-S400</t>
+          <t>Световой поток</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>достаточен для диагностики и многих операций</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>500 часов</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>мощный, для хирургии</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Осветитель эндоскопический 180 Вт Xenon MGB MS-L</t>
+          <t>Примеры</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MGB</t>
+          <t>Mindray HB300L/HB200L, HUGER LLS-2100P, Крыло КРО 1001С</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Класс I, тип BF</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Осветитель эндоскопический MGB MS-LED</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>MGB</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Класс I, тип BF</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Осветитель эндоскопический НПФ Крыло КРО 1001</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>67299</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>MGB Xenon 180 Вт, MGB ML-L 300 Вт</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3998,7 +3936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4324,12 +4262,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Проверьте разъём под световод</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается осветители эндоскопические: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Осветитель работает в связке со световодным кабелем, и типы разъёмов различаются: Karl Storz, Richard Wolf, Olympus и другие. Сначала уточняют, какой световод уже есть в отделении, и подбирают осветитель под его разъём — или планируют кабель под выбранный источник. Несовпадение разъёма делает осветитель неработоспособным без переходника, поэтому это проверяют первым.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4369,12 +4307,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите тип источника света</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>По источнику осветители делят на светодиодные (LED), ксеноновые и галогенные. LED-модели (Mindray HB300L и HB200L, HUGER LLS-2100P, НПФ Крыло КРО 1001С) служат дольше и потребляют меньше энергии. Ксеноновые и галогенные (MGB Xenon 180 Вт, MGB ML-L 300 Вт) дают мощный поток, но лампа расходуется быстрее. Тип источника выбирают под задачи и бюджет эксплуатации.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -4414,12 +4352,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Оцените ресурс источника</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Производитель, Класс и тип безопасности, Время работы, часов, Источник света. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>У светодиодных моделей ресурс диода измеряется десятками тысяч часов: Mindray HB300L — 60 000 часов, HB200L — 20 000 часов. У ламповых источников ресурс лампы ниже и требует периодической замены. Ресурс напрямую влияет на стоимость владения и частоту обслуживания. Значения сверяют по спецификации конкретной модели, поскольку они заметно различаются.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4459,12 +4397,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Определите нужный световой поток</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Mindray, GE, Olympus, MGB, Pentax.</t>
+          <t>Требуемая яркость зависит от задачи: для диагностических процедур обычно достаточно меньшего светового потока, для хирургических вмешательств выбирают более мощные источники. Конкретное значение в люксах уточняют по спецификации выбранной модели и согласуют с типом эндоскопа и характером процедур. Профиль применения отделения определяет, какой запас по яркости нужен.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4504,12 +4442,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите цветовую температуру и регулировку</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Цветовая температура влияет на восприятие тканей: у светодиодных Mindray HB300L и HB200L она регулируется в диапазоне 3000–7000 К. Плавная регулировка яркости позволяет адаптировать свет под этап процедуры. Наличие регулировок и диапазон цветовой температуры сверяют по документации модели, поскольку у ламповых и светодиодных источников они различаются.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4549,12 +4487,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте электробезопасность и регистрацию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Класс и тип электробезопасности указывают в характеристиках: модели MGB отнесены к классу I, тип BF. Этот параметр важен для допуска в эксплуатацию. Перед вводом в оборот сверяют действующее регистрационное удостоверение Росздравнадзора на модель, требования к электропитанию и условия сервисной поддержки, а также доступность сменных ламп для ксеноновых и галогенных источников.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4604,7 +4542,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Осветители эндоскопические подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Mindray, GE, Olympus, MGB, Pentax. При выборе обращают внимание на производитель, класс и тип безопасности, время работы, источник света, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Осветитель бесполезен без совместимого световода, поэтому первым делом сверяю тип разъёма под кабель, который уже есть в отделении — Karl Storz, Richard Wolf или Olympus. По источнику света чаще беру светодиодные модели: у Mindray HB300L ресурс диода 60 000 часов против 20 000 у HB200L, и по сравнению с ксеноном они экономичнее и служат дольше. Дальше смотрю на достаточность светового потока под задачу и на класс электробезопасности.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4888,13 +4826,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое осветители эндоскопические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Осветители эндоскопические — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Mindray, GE, Olympus, MGB, Pentax. Подберём вариант под задачи вашего отделения.</t>
+          <t>Эндоскопический осветитель подаёт световой поток по световодному кабелю в осматриваемую полость. По типу источника осветители делят на светодиодные (LED), ксеноновые и галогенные: LED служат дольше и экономичнее, у Mindray HB300L ресурс диода 60 000 часов. Главный практический критерий выбора — совместимость типа разъёма с имеющимся световодом (Karl Storz, Richard Wolf, Olympus). Затем оценивают световой поток под задачу (диагностика или хирургия), цветовую температуру и класс электробезопасности. Технические параметры сверяют по спецификации модели.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4931,13 +4869,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое эндоскопический осветитель</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Производитель, Класс и тип безопасности, Время работы, часов, Источник света), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Эндоскопический осветитель — источник света, который по световодному кабелю подаёт световой поток в осматриваемую полость при эндоскопии. От него зависят яркость, цветопередача и качество визуализации. Осветитель работает в связке со световодом и эндоскопом, а его характеристики подбирают под тип процедур — диагностических или хирургических.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4974,13 +4912,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Типы источников света</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>По источнику осветители делят на светодиодные (LED), ксеноновые и галогенные. Светодиодные модели Mindray HB300L и HB200L, HUGER LLS-2100P и НПФ Крыло служат дольше и экономичнее. Ксеноновые и галогенные MGB (180 и 300 Вт) дают мощный поток, но лампа расходуется быстрее и требует замены. Тип источника выбирают под задачи и стоимость эксплуатации.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5017,13 +4955,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Совместимость и разъёмы</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Ключевой практический критерий — тип разъёма под световодный кабель: Karl Storz, Richard Wolf, Olympus и другие. Осветитель подбирают под имеющийся световод или планируют кабель под выбранный источник. Несовпадение разъёма делает связку неработоспособной без переходника, поэтому совместимость сверяют по документации до приобретения оборудования.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5040,6 +4978,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как выбрать осветитель</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Сначала проверяют разъём под световод, затем выбирают тип источника (LED, ксенон, галоген) и оценивают ресурс: у Mindray HB300L диод рассчитан на 60 000 часов. Далее определяют нужный световой поток под задачу, цветовую температуру и класс электробезопасности. Перед вводом в оборот сверяют регистрационное удостоверение Росздравнадзора и условия сервиса.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>osvetiteli_endoskopicheskie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
